--- a/JsonConverter/ExcelFiles/LevelUPOptionData.xlsx
+++ b/JsonConverter/ExcelFiles/LevelUPOptionData.xlsx
@@ -1,17 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이태영\Desktop\WanderSoul\JsonConverter\ExcelFiles\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12165"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="140">
   <si>
     <t>아이디</t>
   </si>
@@ -417,33 +425,71 @@
   <si>
     <t>MaxReviveCount</t>
   </si>
+  <si>
+    <t>Sprites/UI/Icon/Epic_B_SoulLattice</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/Rare_B_HollowWing</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/Legendary_B_AscendantSoulMoth</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/Rare_A_TidalCoil</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/Rare_A_TidalCoil</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/Legendary_B_AscendantSoulMoth</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="5">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -451,7 +497,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -467,7 +513,13 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -481,46 +533,48 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -528,7 +582,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -718,31 +772,32 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Z1000"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="30.0"/>
-    <col customWidth="1" min="2" max="2" width="20.0"/>
-    <col customWidth="1" min="3" max="3" width="48.0"/>
-    <col customWidth="1" min="4" max="4" width="17.38"/>
-    <col customWidth="1" min="5" max="5" width="9.88"/>
-    <col customWidth="1" min="6" max="7" width="12.0"/>
-    <col customWidth="1" min="8" max="8" width="13.63"/>
-    <col customWidth="1" min="9" max="12" width="20.0"/>
-    <col customWidth="1" min="13" max="13" width="7.63"/>
-    <col customWidth="1" min="14" max="14" width="21.5"/>
-    <col customWidth="1" min="15" max="16" width="9.88"/>
-    <col customWidth="1" min="17" max="26" width="13.0"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="4" max="4" width="17.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="13.625" customWidth="1"/>
+    <col min="9" max="12" width="20" customWidth="1"/>
+    <col min="13" max="13" width="7.625" customWidth="1"/>
+    <col min="14" max="14" width="21.5" customWidth="1"/>
+    <col min="15" max="15" width="9.875" customWidth="1"/>
+    <col min="16" max="16" width="61.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="26" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24.0" customHeight="1">
+    <row r="1" spans="1:26" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -802,7 +857,7 @@
       <c r="Y1" s="4"/>
       <c r="Z1" s="4"/>
     </row>
-    <row r="2" ht="24.0" customHeight="1">
+    <row r="2" spans="1:26" ht="24" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
@@ -862,7 +917,7 @@
       <c r="Y2" s="4"/>
       <c r="Z2" s="4"/>
     </row>
-    <row r="3" ht="24.0" customHeight="1">
+    <row r="3" spans="1:26" ht="24" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -922,7 +977,7 @@
       <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
     </row>
-    <row r="4" ht="31.5" customHeight="1">
+    <row r="4" spans="1:26" ht="31.5" customHeight="1">
       <c r="A4" s="5" t="s">
         <v>35</v>
       </c>
@@ -939,7 +994,7 @@
         <v>39</v>
       </c>
       <c r="F4" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
@@ -957,12 +1012,14 @@
         <v>0.08</v>
       </c>
       <c r="N4" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="O4" s="5">
-        <v>100.0</v>
-      </c>
-      <c r="P4" s="5"/>
+        <v>100</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>134</v>
+      </c>
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
@@ -974,7 +1031,7 @@
       <c r="Y4" s="5"/>
       <c r="Z4" s="5"/>
     </row>
-    <row r="5" ht="31.5" customHeight="1">
+    <row r="5" spans="1:26" ht="31.5" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>43</v>
       </c>
@@ -991,7 +1048,7 @@
         <v>46</v>
       </c>
       <c r="F5" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
@@ -1009,12 +1066,14 @@
         <v>0.12</v>
       </c>
       <c r="N5" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O5" s="5">
-        <v>45.0</v>
-      </c>
-      <c r="P5" s="5"/>
+        <v>45</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>135</v>
+      </c>
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
@@ -1026,7 +1085,7 @@
       <c r="Y5" s="5"/>
       <c r="Z5" s="5"/>
     </row>
-    <row r="6" ht="31.5" customHeight="1">
+    <row r="6" spans="1:26" ht="31.5" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>47</v>
       </c>
@@ -1043,7 +1102,7 @@
         <v>50</v>
       </c>
       <c r="F6" s="5">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
@@ -1061,12 +1120,14 @@
         <v>0.18</v>
       </c>
       <c r="N6" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="O6" s="5">
-        <v>18.0</v>
-      </c>
-      <c r="P6" s="5"/>
+        <v>18</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>136</v>
+      </c>
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
       <c r="S6" s="5"/>
@@ -1078,7 +1139,7 @@
       <c r="Y6" s="5"/>
       <c r="Z6" s="5"/>
     </row>
-    <row r="7" ht="31.5" customHeight="1">
+    <row r="7" spans="1:26" ht="31.5" customHeight="1">
       <c r="A7" s="5" t="s">
         <v>51</v>
       </c>
@@ -1095,7 +1156,7 @@
         <v>54</v>
       </c>
       <c r="F7" s="5">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
@@ -1113,12 +1174,14 @@
         <v>0.25</v>
       </c>
       <c r="N7" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O7" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="P7" s="5"/>
+        <v>5</v>
+      </c>
+      <c r="P7" s="5" t="s">
+        <v>137</v>
+      </c>
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
       <c r="S7" s="5"/>
@@ -1130,7 +1193,7 @@
       <c r="Y7" s="5"/>
       <c r="Z7" s="5"/>
     </row>
-    <row r="8" ht="31.5" customHeight="1">
+    <row r="8" spans="1:26" ht="31.5" customHeight="1">
       <c r="A8" s="5" t="s">
         <v>55</v>
       </c>
@@ -1147,7 +1210,7 @@
         <v>39</v>
       </c>
       <c r="F8" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
@@ -1165,12 +1228,14 @@
         <v>0.06</v>
       </c>
       <c r="N8" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="O8" s="5">
-        <v>100.0</v>
-      </c>
-      <c r="P8" s="5"/>
+        <v>100</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>134</v>
+      </c>
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
       <c r="S8" s="5"/>
@@ -1182,7 +1247,7 @@
       <c r="Y8" s="5"/>
       <c r="Z8" s="5"/>
     </row>
-    <row r="9" ht="31.5" customHeight="1">
+    <row r="9" spans="1:26" ht="31.5" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>60</v>
       </c>
@@ -1199,7 +1264,7 @@
         <v>46</v>
       </c>
       <c r="F9" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
@@ -1217,12 +1282,14 @@
         <v>0.1</v>
       </c>
       <c r="N9" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O9" s="5">
-        <v>45.0</v>
-      </c>
-      <c r="P9" s="5"/>
+        <v>45</v>
+      </c>
+      <c r="P9" s="5" t="s">
+        <v>135</v>
+      </c>
       <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
       <c r="S9" s="5"/>
@@ -1234,7 +1301,7 @@
       <c r="Y9" s="5"/>
       <c r="Z9" s="5"/>
     </row>
-    <row r="10" ht="31.5" customHeight="1">
+    <row r="10" spans="1:26" ht="31.5" customHeight="1">
       <c r="A10" s="5" t="s">
         <v>63</v>
       </c>
@@ -1251,7 +1318,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="5">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
@@ -1269,12 +1336,14 @@
         <v>0.15</v>
       </c>
       <c r="N10" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="O10" s="5">
-        <v>18.0</v>
-      </c>
-      <c r="P10" s="5"/>
+        <v>18</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>136</v>
+      </c>
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
       <c r="S10" s="5"/>
@@ -1286,7 +1355,7 @@
       <c r="Y10" s="5"/>
       <c r="Z10" s="5"/>
     </row>
-    <row r="11" ht="31.5" customHeight="1">
+    <row r="11" spans="1:26" ht="31.5" customHeight="1">
       <c r="A11" s="5" t="s">
         <v>66</v>
       </c>
@@ -1303,7 +1372,7 @@
         <v>54</v>
       </c>
       <c r="F11" s="5">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
@@ -1321,12 +1390,14 @@
         <v>0.22</v>
       </c>
       <c r="N11" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O11" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="P11" s="5"/>
+        <v>5</v>
+      </c>
+      <c r="P11" s="5" t="s">
+        <v>137</v>
+      </c>
       <c r="Q11" s="5"/>
       <c r="R11" s="5"/>
       <c r="S11" s="5"/>
@@ -1338,7 +1409,7 @@
       <c r="Y11" s="5"/>
       <c r="Z11" s="5"/>
     </row>
-    <row r="12" ht="31.5" customHeight="1">
+    <row r="12" spans="1:26" ht="31.5" customHeight="1">
       <c r="A12" s="5" t="s">
         <v>69</v>
       </c>
@@ -1355,7 +1426,7 @@
         <v>39</v>
       </c>
       <c r="F12" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
@@ -1373,12 +1444,14 @@
         <v>0.15</v>
       </c>
       <c r="N12" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="O12" s="5">
-        <v>100.0</v>
-      </c>
-      <c r="P12" s="5"/>
+        <v>100</v>
+      </c>
+      <c r="P12" s="5" t="s">
+        <v>134</v>
+      </c>
       <c r="Q12" s="5"/>
       <c r="R12" s="5"/>
       <c r="S12" s="5"/>
@@ -1390,7 +1463,7 @@
       <c r="Y12" s="5"/>
       <c r="Z12" s="5"/>
     </row>
-    <row r="13" ht="31.5" customHeight="1">
+    <row r="13" spans="1:26" ht="31.5" customHeight="1">
       <c r="A13" s="5" t="s">
         <v>73</v>
       </c>
@@ -1407,7 +1480,7 @@
         <v>46</v>
       </c>
       <c r="F13" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -1425,12 +1498,14 @@
         <v>0.25</v>
       </c>
       <c r="N13" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O13" s="5">
-        <v>45.0</v>
-      </c>
-      <c r="P13" s="5"/>
+        <v>45</v>
+      </c>
+      <c r="P13" s="5" t="s">
+        <v>135</v>
+      </c>
       <c r="Q13" s="5"/>
       <c r="R13" s="5"/>
       <c r="S13" s="5"/>
@@ -1442,7 +1517,7 @@
       <c r="Y13" s="5"/>
       <c r="Z13" s="5"/>
     </row>
-    <row r="14" ht="31.5" customHeight="1">
+    <row r="14" spans="1:26" ht="31.5" customHeight="1">
       <c r="A14" s="5" t="s">
         <v>76</v>
       </c>
@@ -1459,7 +1534,7 @@
         <v>50</v>
       </c>
       <c r="F14" s="5">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
@@ -1477,12 +1552,14 @@
         <v>0.4</v>
       </c>
       <c r="N14" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="O14" s="5">
-        <v>18.0</v>
-      </c>
-      <c r="P14" s="5"/>
+        <v>18</v>
+      </c>
+      <c r="P14" s="5" t="s">
+        <v>136</v>
+      </c>
       <c r="Q14" s="5"/>
       <c r="R14" s="5"/>
       <c r="S14" s="5"/>
@@ -1494,7 +1571,7 @@
       <c r="Y14" s="5"/>
       <c r="Z14" s="5"/>
     </row>
-    <row r="15" ht="31.5" customHeight="1">
+    <row r="15" spans="1:26" ht="31.5" customHeight="1">
       <c r="A15" s="5" t="s">
         <v>79</v>
       </c>
@@ -1511,7 +1588,7 @@
         <v>54</v>
       </c>
       <c r="F15" s="5">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
@@ -1529,12 +1606,14 @@
         <v>0.6</v>
       </c>
       <c r="N15" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O15" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="P15" s="5"/>
+        <v>5</v>
+      </c>
+      <c r="P15" s="5" t="s">
+        <v>137</v>
+      </c>
       <c r="Q15" s="5"/>
       <c r="R15" s="5"/>
       <c r="S15" s="5"/>
@@ -1546,7 +1625,7 @@
       <c r="Y15" s="5"/>
       <c r="Z15" s="5"/>
     </row>
-    <row r="16" ht="31.5" customHeight="1">
+    <row r="16" spans="1:26" ht="31.5" customHeight="1">
       <c r="A16" s="5" t="s">
         <v>82</v>
       </c>
@@ -1563,7 +1642,7 @@
         <v>39</v>
       </c>
       <c r="F16" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
@@ -1581,12 +1660,14 @@
         <v>0.15</v>
       </c>
       <c r="N16" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="O16" s="5">
-        <v>100.0</v>
-      </c>
-      <c r="P16" s="5"/>
+        <v>100</v>
+      </c>
+      <c r="P16" s="5" t="s">
+        <v>134</v>
+      </c>
       <c r="Q16" s="5"/>
       <c r="R16" s="5"/>
       <c r="S16" s="5"/>
@@ -1598,7 +1679,7 @@
       <c r="Y16" s="5"/>
       <c r="Z16" s="5"/>
     </row>
-    <row r="17" ht="31.5" customHeight="1">
+    <row r="17" spans="1:26" ht="31.5" customHeight="1">
       <c r="A17" s="5" t="s">
         <v>86</v>
       </c>
@@ -1615,7 +1696,7 @@
         <v>46</v>
       </c>
       <c r="F17" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
@@ -1633,12 +1714,14 @@
         <v>0.25</v>
       </c>
       <c r="N17" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O17" s="5">
-        <v>45.0</v>
-      </c>
-      <c r="P17" s="5"/>
+        <v>45</v>
+      </c>
+      <c r="P17" s="5" t="s">
+        <v>135</v>
+      </c>
       <c r="Q17" s="5"/>
       <c r="R17" s="5"/>
       <c r="S17" s="5"/>
@@ -1650,7 +1733,7 @@
       <c r="Y17" s="5"/>
       <c r="Z17" s="5"/>
     </row>
-    <row r="18" ht="31.5" customHeight="1">
+    <row r="18" spans="1:26" ht="31.5" customHeight="1">
       <c r="A18" s="5" t="s">
         <v>89</v>
       </c>
@@ -1667,7 +1750,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="5">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
@@ -1685,12 +1768,14 @@
         <v>0.4</v>
       </c>
       <c r="N18" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="O18" s="5">
-        <v>18.0</v>
-      </c>
-      <c r="P18" s="5"/>
+        <v>18</v>
+      </c>
+      <c r="P18" s="5" t="s">
+        <v>136</v>
+      </c>
       <c r="Q18" s="5"/>
       <c r="R18" s="5"/>
       <c r="S18" s="5"/>
@@ -1702,7 +1787,7 @@
       <c r="Y18" s="5"/>
       <c r="Z18" s="5"/>
     </row>
-    <row r="19" ht="31.5" customHeight="1">
+    <row r="19" spans="1:26" ht="31.5" customHeight="1">
       <c r="A19" s="5" t="s">
         <v>92</v>
       </c>
@@ -1719,7 +1804,7 @@
         <v>54</v>
       </c>
       <c r="F19" s="5">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
@@ -1737,12 +1822,14 @@
         <v>0.6</v>
       </c>
       <c r="N19" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O19" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="P19" s="5"/>
+        <v>5</v>
+      </c>
+      <c r="P19" s="5" t="s">
+        <v>137</v>
+      </c>
       <c r="Q19" s="5"/>
       <c r="R19" s="5"/>
       <c r="S19" s="5"/>
@@ -1754,7 +1841,7 @@
       <c r="Y19" s="5"/>
       <c r="Z19" s="5"/>
     </row>
-    <row r="20" ht="31.5" customHeight="1">
+    <row r="20" spans="1:26" ht="31.5" customHeight="1">
       <c r="A20" s="5" t="s">
         <v>95</v>
       </c>
@@ -1771,7 +1858,7 @@
         <v>39</v>
       </c>
       <c r="F20" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
@@ -1789,12 +1876,14 @@
         <v>0.3</v>
       </c>
       <c r="N20" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="O20" s="5">
-        <v>100.0</v>
-      </c>
-      <c r="P20" s="5"/>
+        <v>100</v>
+      </c>
+      <c r="P20" s="5" t="s">
+        <v>134</v>
+      </c>
       <c r="Q20" s="5"/>
       <c r="R20" s="5"/>
       <c r="S20" s="5"/>
@@ -1806,7 +1895,7 @@
       <c r="Y20" s="5"/>
       <c r="Z20" s="5"/>
     </row>
-    <row r="21" ht="31.5" customHeight="1">
+    <row r="21" spans="1:26" ht="31.5" customHeight="1">
       <c r="A21" s="5" t="s">
         <v>99</v>
       </c>
@@ -1823,7 +1912,7 @@
         <v>46</v>
       </c>
       <c r="F21" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
@@ -1841,12 +1930,14 @@
         <v>0.5</v>
       </c>
       <c r="N21" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O21" s="5">
-        <v>45.0</v>
-      </c>
-      <c r="P21" s="5"/>
+        <v>45</v>
+      </c>
+      <c r="P21" s="5" t="s">
+        <v>135</v>
+      </c>
       <c r="Q21" s="5"/>
       <c r="R21" s="5"/>
       <c r="S21" s="5"/>
@@ -1858,7 +1949,7 @@
       <c r="Y21" s="5"/>
       <c r="Z21" s="5"/>
     </row>
-    <row r="22" ht="31.5" customHeight="1">
+    <row r="22" spans="1:26" ht="31.5" customHeight="1">
       <c r="A22" s="5" t="s">
         <v>102</v>
       </c>
@@ -1875,7 +1966,7 @@
         <v>50</v>
       </c>
       <c r="F22" s="5">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -1893,12 +1984,14 @@
         <v>0.8</v>
       </c>
       <c r="N22" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="O22" s="5">
-        <v>18.0</v>
-      </c>
-      <c r="P22" s="5"/>
+        <v>18</v>
+      </c>
+      <c r="P22" s="5" t="s">
+        <v>136</v>
+      </c>
       <c r="Q22" s="5"/>
       <c r="R22" s="5"/>
       <c r="S22" s="5"/>
@@ -1910,7 +2003,7 @@
       <c r="Y22" s="5"/>
       <c r="Z22" s="5"/>
     </row>
-    <row r="23" ht="31.5" customHeight="1">
+    <row r="23" spans="1:26" ht="31.5" customHeight="1">
       <c r="A23" s="5" t="s">
         <v>105</v>
       </c>
@@ -1927,7 +2020,7 @@
         <v>54</v>
       </c>
       <c r="F23" s="5">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
@@ -1945,12 +2038,14 @@
         <v>1.2</v>
       </c>
       <c r="N23" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O23" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="P23" s="5"/>
+        <v>5</v>
+      </c>
+      <c r="P23" s="5" t="s">
+        <v>137</v>
+      </c>
       <c r="Q23" s="5"/>
       <c r="R23" s="5"/>
       <c r="S23" s="5"/>
@@ -1962,7 +2057,7 @@
       <c r="Y23" s="5"/>
       <c r="Z23" s="5"/>
     </row>
-    <row r="24" ht="31.5" customHeight="1">
+    <row r="24" spans="1:26" ht="31.5" customHeight="1">
       <c r="A24" s="5" t="s">
         <v>108</v>
       </c>
@@ -1979,7 +2074,7 @@
         <v>39</v>
       </c>
       <c r="F24" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
@@ -1997,12 +2092,14 @@
         <v>0.5</v>
       </c>
       <c r="N24" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="O24" s="5">
-        <v>100.0</v>
-      </c>
-      <c r="P24" s="5"/>
+        <v>100</v>
+      </c>
+      <c r="P24" s="5" t="s">
+        <v>134</v>
+      </c>
       <c r="Q24" s="5"/>
       <c r="R24" s="5"/>
       <c r="S24" s="5"/>
@@ -2014,7 +2111,7 @@
       <c r="Y24" s="5"/>
       <c r="Z24" s="5"/>
     </row>
-    <row r="25" ht="31.5" customHeight="1">
+    <row r="25" spans="1:26" ht="31.5" customHeight="1">
       <c r="A25" s="5" t="s">
         <v>112</v>
       </c>
@@ -2031,7 +2128,7 @@
         <v>46</v>
       </c>
       <c r="F25" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
@@ -2049,12 +2146,14 @@
         <v>0.8</v>
       </c>
       <c r="N25" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O25" s="5">
-        <v>45.0</v>
-      </c>
-      <c r="P25" s="5"/>
+        <v>45</v>
+      </c>
+      <c r="P25" s="5" t="s">
+        <v>135</v>
+      </c>
       <c r="Q25" s="5"/>
       <c r="R25" s="5"/>
       <c r="S25" s="5"/>
@@ -2066,7 +2165,7 @@
       <c r="Y25" s="5"/>
       <c r="Z25" s="5"/>
     </row>
-    <row r="26" ht="31.5" customHeight="1">
+    <row r="26" spans="1:26" ht="31.5" customHeight="1">
       <c r="A26" s="5" t="s">
         <v>115</v>
       </c>
@@ -2083,7 +2182,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="5">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
@@ -2101,12 +2200,14 @@
         <v>1.2</v>
       </c>
       <c r="N26" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="O26" s="5">
-        <v>18.0</v>
-      </c>
-      <c r="P26" s="5"/>
+        <v>18</v>
+      </c>
+      <c r="P26" s="5" t="s">
+        <v>136</v>
+      </c>
       <c r="Q26" s="5"/>
       <c r="R26" s="5"/>
       <c r="S26" s="5"/>
@@ -2118,7 +2219,7 @@
       <c r="Y26" s="5"/>
       <c r="Z26" s="5"/>
     </row>
-    <row r="27" ht="31.5" customHeight="1">
+    <row r="27" spans="1:26" ht="31.5" customHeight="1">
       <c r="A27" s="5" t="s">
         <v>118</v>
       </c>
@@ -2135,7 +2236,7 @@
         <v>54</v>
       </c>
       <c r="F27" s="5">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
@@ -2153,12 +2254,14 @@
         <v>1.8</v>
       </c>
       <c r="N27" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O27" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="P27" s="5"/>
+        <v>5</v>
+      </c>
+      <c r="P27" s="5" t="s">
+        <v>137</v>
+      </c>
       <c r="Q27" s="5"/>
       <c r="R27" s="5"/>
       <c r="S27" s="5"/>
@@ -2170,7 +2273,7 @@
       <c r="Y27" s="5"/>
       <c r="Z27" s="5"/>
     </row>
-    <row r="28" ht="31.5" customHeight="1">
+    <row r="28" spans="1:26" ht="31.5" customHeight="1">
       <c r="A28" s="5" t="s">
         <v>121</v>
       </c>
@@ -2187,7 +2290,7 @@
         <v>50</v>
       </c>
       <c r="F28" s="5">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
@@ -2202,15 +2305,17 @@
         <v>59</v>
       </c>
       <c r="M28" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N28" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O28" s="5">
-        <v>8.0</v>
-      </c>
-      <c r="P28" s="5"/>
+        <v>8</v>
+      </c>
+      <c r="P28" s="5" t="s">
+        <v>139</v>
+      </c>
       <c r="Q28" s="5"/>
       <c r="R28" s="5"/>
       <c r="S28" s="5"/>
@@ -2222,7 +2327,7 @@
       <c r="Y28" s="5"/>
       <c r="Z28" s="5"/>
     </row>
-    <row r="29" ht="31.5" customHeight="1">
+    <row r="29" spans="1:26" ht="31.5" customHeight="1">
       <c r="A29" s="5" t="s">
         <v>126</v>
       </c>
@@ -2239,7 +2344,7 @@
         <v>54</v>
       </c>
       <c r="F29" s="5">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
@@ -2251,12 +2356,14 @@
       <c r="L29" s="5"/>
       <c r="M29" s="5"/>
       <c r="N29" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="O29" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="P29" s="5"/>
+        <v>2</v>
+      </c>
+      <c r="P29" s="5" t="s">
+        <v>138</v>
+      </c>
       <c r="Q29" s="5"/>
       <c r="R29" s="5"/>
       <c r="S29" s="5"/>
@@ -2268,7 +2375,7 @@
       <c r="Y29" s="5"/>
       <c r="Z29" s="5"/>
     </row>
-    <row r="30" ht="31.5" customHeight="1">
+    <row r="30" spans="1:26" ht="31.5" customHeight="1">
       <c r="A30" s="5" t="s">
         <v>130</v>
       </c>
@@ -2285,7 +2392,7 @@
         <v>54</v>
       </c>
       <c r="F30" s="5">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
@@ -2300,15 +2407,17 @@
         <v>59</v>
       </c>
       <c r="M30" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N30" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="O30" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="P30" s="5"/>
+        <v>2</v>
+      </c>
+      <c r="P30" s="5" t="s">
+        <v>137</v>
+      </c>
       <c r="Q30" s="5"/>
       <c r="R30" s="5"/>
       <c r="S30" s="5"/>
@@ -2320,7 +2429,7 @@
       <c r="Y30" s="5"/>
       <c r="Z30" s="5"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="1:26" ht="15.75" customHeight="1">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -2348,7 +2457,7 @@
       <c r="Y31" s="5"/>
       <c r="Z31" s="5"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="1:26" ht="15.75" customHeight="1">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -2376,7 +2485,7 @@
       <c r="Y32" s="5"/>
       <c r="Z32" s="5"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="1:26" ht="15.75" customHeight="1">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -2404,7 +2513,7 @@
       <c r="Y33" s="5"/>
       <c r="Z33" s="5"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" spans="1:26" ht="15.75" customHeight="1">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -2432,7 +2541,7 @@
       <c r="Y34" s="5"/>
       <c r="Z34" s="5"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" spans="1:26" ht="15.75" customHeight="1">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -2460,7 +2569,7 @@
       <c r="Y35" s="5"/>
       <c r="Z35" s="5"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" spans="1:26" ht="15.75" customHeight="1">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -2488,7 +2597,7 @@
       <c r="Y36" s="5"/>
       <c r="Z36" s="5"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" spans="1:26" ht="15.75" customHeight="1">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -2516,7 +2625,7 @@
       <c r="Y37" s="5"/>
       <c r="Z37" s="5"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" spans="1:26" ht="15.75" customHeight="1">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -2544,7 +2653,7 @@
       <c r="Y38" s="5"/>
       <c r="Z38" s="5"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" spans="1:26" ht="15.75" customHeight="1">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -2572,7 +2681,7 @@
       <c r="Y39" s="5"/>
       <c r="Z39" s="5"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" spans="1:26" ht="15.75" customHeight="1">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -2600,7 +2709,7 @@
       <c r="Y40" s="5"/>
       <c r="Z40" s="5"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" spans="1:26" ht="15.75" customHeight="1">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -2628,7 +2737,7 @@
       <c r="Y41" s="5"/>
       <c r="Z41" s="5"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" spans="1:26" ht="15.75" customHeight="1">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -2656,7 +2765,7 @@
       <c r="Y42" s="5"/>
       <c r="Z42" s="5"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" spans="1:26" ht="15.75" customHeight="1">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -2684,7 +2793,7 @@
       <c r="Y43" s="5"/>
       <c r="Z43" s="5"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" spans="1:26" ht="15.75" customHeight="1">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -2712,7 +2821,7 @@
       <c r="Y44" s="5"/>
       <c r="Z44" s="5"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" spans="1:26" ht="15.75" customHeight="1">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -2740,7 +2849,7 @@
       <c r="Y45" s="5"/>
       <c r="Z45" s="5"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" spans="1:26" ht="15.75" customHeight="1">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -2768,7 +2877,7 @@
       <c r="Y46" s="5"/>
       <c r="Z46" s="5"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" spans="1:26" ht="15.75" customHeight="1">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -2796,7 +2905,7 @@
       <c r="Y47" s="5"/>
       <c r="Z47" s="5"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="1:26" ht="15.75" customHeight="1">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -2824,7 +2933,7 @@
       <c r="Y48" s="5"/>
       <c r="Z48" s="5"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="1:26" ht="15.75" customHeight="1">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -2852,7 +2961,7 @@
       <c r="Y49" s="5"/>
       <c r="Z49" s="5"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" spans="1:26" ht="15.75" customHeight="1">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
@@ -2880,7 +2989,7 @@
       <c r="Y50" s="5"/>
       <c r="Z50" s="5"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" spans="1:26" ht="15.75" customHeight="1">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -2908,7 +3017,7 @@
       <c r="Y51" s="5"/>
       <c r="Z51" s="5"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" spans="1:26" ht="15.75" customHeight="1">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -2936,7 +3045,7 @@
       <c r="Y52" s="5"/>
       <c r="Z52" s="5"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" spans="1:26" ht="15.75" customHeight="1">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
@@ -2964,7 +3073,7 @@
       <c r="Y53" s="5"/>
       <c r="Z53" s="5"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" spans="1:26" ht="15.75" customHeight="1">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -2992,7 +3101,7 @@
       <c r="Y54" s="5"/>
       <c r="Z54" s="5"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" spans="1:26" ht="15.75" customHeight="1">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -3020,7 +3129,7 @@
       <c r="Y55" s="5"/>
       <c r="Z55" s="5"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" spans="1:26" ht="15.75" customHeight="1">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -3048,7 +3157,7 @@
       <c r="Y56" s="5"/>
       <c r="Z56" s="5"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" spans="1:26" ht="15.75" customHeight="1">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -3076,7 +3185,7 @@
       <c r="Y57" s="5"/>
       <c r="Z57" s="5"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" spans="1:26" ht="15.75" customHeight="1">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -3104,7 +3213,7 @@
       <c r="Y58" s="5"/>
       <c r="Z58" s="5"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" spans="1:26" ht="15.75" customHeight="1">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -3132,7 +3241,7 @@
       <c r="Y59" s="5"/>
       <c r="Z59" s="5"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" spans="1:26" ht="15.75" customHeight="1">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -3160,7 +3269,7 @@
       <c r="Y60" s="5"/>
       <c r="Z60" s="5"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" spans="1:26" ht="15.75" customHeight="1">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -3188,7 +3297,7 @@
       <c r="Y61" s="5"/>
       <c r="Z61" s="5"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" spans="1:26" ht="15.75" customHeight="1">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -3216,7 +3325,7 @@
       <c r="Y62" s="5"/>
       <c r="Z62" s="5"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" spans="1:26" ht="15.75" customHeight="1">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
@@ -3244,7 +3353,7 @@
       <c r="Y63" s="5"/>
       <c r="Z63" s="5"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" spans="1:26" ht="15.75" customHeight="1">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
@@ -3272,7 +3381,7 @@
       <c r="Y64" s="5"/>
       <c r="Z64" s="5"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" spans="1:26" ht="15.75" customHeight="1">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -3300,7 +3409,7 @@
       <c r="Y65" s="5"/>
       <c r="Z65" s="5"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" spans="1:26" ht="15.75" customHeight="1">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -3328,7 +3437,7 @@
       <c r="Y66" s="5"/>
       <c r="Z66" s="5"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" spans="1:26" ht="15.75" customHeight="1">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
@@ -3356,7 +3465,7 @@
       <c r="Y67" s="5"/>
       <c r="Z67" s="5"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" spans="1:26" ht="15.75" customHeight="1">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
@@ -3384,7 +3493,7 @@
       <c r="Y68" s="5"/>
       <c r="Z68" s="5"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" spans="1:26" ht="15.75" customHeight="1">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
@@ -3412,7 +3521,7 @@
       <c r="Y69" s="5"/>
       <c r="Z69" s="5"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" spans="1:26" ht="15.75" customHeight="1">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
@@ -3440,7 +3549,7 @@
       <c r="Y70" s="5"/>
       <c r="Z70" s="5"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" spans="1:26" ht="15.75" customHeight="1">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
@@ -3468,7 +3577,7 @@
       <c r="Y71" s="5"/>
       <c r="Z71" s="5"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" spans="1:26" ht="15.75" customHeight="1">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
@@ -3496,7 +3605,7 @@
       <c r="Y72" s="5"/>
       <c r="Z72" s="5"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" spans="1:26" ht="15.75" customHeight="1">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
@@ -3524,7 +3633,7 @@
       <c r="Y73" s="5"/>
       <c r="Z73" s="5"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" spans="1:26" ht="15.75" customHeight="1">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
@@ -3552,7 +3661,7 @@
       <c r="Y74" s="5"/>
       <c r="Z74" s="5"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" spans="1:26" ht="15.75" customHeight="1">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
@@ -3580,7 +3689,7 @@
       <c r="Y75" s="5"/>
       <c r="Z75" s="5"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" spans="1:26" ht="15.75" customHeight="1">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -3608,7 +3717,7 @@
       <c r="Y76" s="5"/>
       <c r="Z76" s="5"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" spans="1:26" ht="15.75" customHeight="1">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
@@ -3636,7 +3745,7 @@
       <c r="Y77" s="5"/>
       <c r="Z77" s="5"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" spans="1:26" ht="15.75" customHeight="1">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
@@ -3664,7 +3773,7 @@
       <c r="Y78" s="5"/>
       <c r="Z78" s="5"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" spans="1:26" ht="15.75" customHeight="1">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
@@ -3692,7 +3801,7 @@
       <c r="Y79" s="5"/>
       <c r="Z79" s="5"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" spans="1:26" ht="15.75" customHeight="1">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
@@ -3720,7 +3829,7 @@
       <c r="Y80" s="5"/>
       <c r="Z80" s="5"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" spans="1:26" ht="15.75" customHeight="1">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
@@ -3748,7 +3857,7 @@
       <c r="Y81" s="5"/>
       <c r="Z81" s="5"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" spans="1:26" ht="15.75" customHeight="1">
       <c r="A82" s="5"/>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
@@ -3776,7 +3885,7 @@
       <c r="Y82" s="5"/>
       <c r="Z82" s="5"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" spans="1:26" ht="15.75" customHeight="1">
       <c r="A83" s="5"/>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -3804,7 +3913,7 @@
       <c r="Y83" s="5"/>
       <c r="Z83" s="5"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" spans="1:26" ht="15.75" customHeight="1">
       <c r="A84" s="5"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
@@ -3832,7 +3941,7 @@
       <c r="Y84" s="5"/>
       <c r="Z84" s="5"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" spans="1:26" ht="15.75" customHeight="1">
       <c r="A85" s="5"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
@@ -3860,7 +3969,7 @@
       <c r="Y85" s="5"/>
       <c r="Z85" s="5"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" spans="1:26" ht="15.75" customHeight="1">
       <c r="A86" s="5"/>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
@@ -3888,7 +3997,7 @@
       <c r="Y86" s="5"/>
       <c r="Z86" s="5"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" spans="1:26" ht="15.75" customHeight="1">
       <c r="A87" s="5"/>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
@@ -3916,7 +4025,7 @@
       <c r="Y87" s="5"/>
       <c r="Z87" s="5"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" spans="1:26" ht="15.75" customHeight="1">
       <c r="A88" s="5"/>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
@@ -3944,7 +4053,7 @@
       <c r="Y88" s="5"/>
       <c r="Z88" s="5"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" spans="1:26" ht="15.75" customHeight="1">
       <c r="A89" s="5"/>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
@@ -3972,7 +4081,7 @@
       <c r="Y89" s="5"/>
       <c r="Z89" s="5"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" spans="1:26" ht="15.75" customHeight="1">
       <c r="A90" s="5"/>
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
@@ -4000,7 +4109,7 @@
       <c r="Y90" s="5"/>
       <c r="Z90" s="5"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" spans="1:26" ht="15.75" customHeight="1">
       <c r="A91" s="5"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
@@ -4028,7 +4137,7 @@
       <c r="Y91" s="5"/>
       <c r="Z91" s="5"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" spans="1:26" ht="15.75" customHeight="1">
       <c r="A92" s="5"/>
       <c r="B92" s="5"/>
       <c r="C92" s="5"/>
@@ -4056,7 +4165,7 @@
       <c r="Y92" s="5"/>
       <c r="Z92" s="5"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" spans="1:26" ht="15.75" customHeight="1">
       <c r="A93" s="5"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
@@ -4084,7 +4193,7 @@
       <c r="Y93" s="5"/>
       <c r="Z93" s="5"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" spans="1:26" ht="15.75" customHeight="1">
       <c r="A94" s="5"/>
       <c r="B94" s="5"/>
       <c r="C94" s="5"/>
@@ -4112,7 +4221,7 @@
       <c r="Y94" s="5"/>
       <c r="Z94" s="5"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" spans="1:26" ht="15.75" customHeight="1">
       <c r="A95" s="5"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
@@ -4140,7 +4249,7 @@
       <c r="Y95" s="5"/>
       <c r="Z95" s="5"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" spans="1:26" ht="15.75" customHeight="1">
       <c r="A96" s="5"/>
       <c r="B96" s="5"/>
       <c r="C96" s="5"/>
@@ -4168,7 +4277,7 @@
       <c r="Y96" s="5"/>
       <c r="Z96" s="5"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" spans="1:26" ht="15.75" customHeight="1">
       <c r="A97" s="5"/>
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
@@ -4196,7 +4305,7 @@
       <c r="Y97" s="5"/>
       <c r="Z97" s="5"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" spans="1:26" ht="15.75" customHeight="1">
       <c r="A98" s="5"/>
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
@@ -4224,7 +4333,7 @@
       <c r="Y98" s="5"/>
       <c r="Z98" s="5"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" spans="1:26" ht="15.75" customHeight="1">
       <c r="A99" s="5"/>
       <c r="B99" s="5"/>
       <c r="C99" s="5"/>
@@ -4252,7 +4361,7 @@
       <c r="Y99" s="5"/>
       <c r="Z99" s="5"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" spans="1:26" ht="15.75" customHeight="1">
       <c r="A100" s="5"/>
       <c r="B100" s="5"/>
       <c r="C100" s="5"/>
@@ -4280,7 +4389,7 @@
       <c r="Y100" s="5"/>
       <c r="Z100" s="5"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" spans="1:26" ht="15.75" customHeight="1">
       <c r="A101" s="5"/>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
@@ -4308,7 +4417,7 @@
       <c r="Y101" s="5"/>
       <c r="Z101" s="5"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" spans="1:26" ht="15.75" customHeight="1">
       <c r="A102" s="5"/>
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
@@ -4336,7 +4445,7 @@
       <c r="Y102" s="5"/>
       <c r="Z102" s="5"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" spans="1:26" ht="15.75" customHeight="1">
       <c r="A103" s="5"/>
       <c r="B103" s="5"/>
       <c r="C103" s="5"/>
@@ -4364,7 +4473,7 @@
       <c r="Y103" s="5"/>
       <c r="Z103" s="5"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" spans="1:26" ht="15.75" customHeight="1">
       <c r="A104" s="5"/>
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
@@ -4392,7 +4501,7 @@
       <c r="Y104" s="5"/>
       <c r="Z104" s="5"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" spans="1:26" ht="15.75" customHeight="1">
       <c r="A105" s="5"/>
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
@@ -4420,7 +4529,7 @@
       <c r="Y105" s="5"/>
       <c r="Z105" s="5"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" spans="1:26" ht="15.75" customHeight="1">
       <c r="A106" s="5"/>
       <c r="B106" s="5"/>
       <c r="C106" s="5"/>
@@ -4448,7 +4557,7 @@
       <c r="Y106" s="5"/>
       <c r="Z106" s="5"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row r="107" spans="1:26" ht="15.75" customHeight="1">
       <c r="A107" s="5"/>
       <c r="B107" s="5"/>
       <c r="C107" s="5"/>
@@ -4476,7 +4585,7 @@
       <c r="Y107" s="5"/>
       <c r="Z107" s="5"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" spans="1:26" ht="15.75" customHeight="1">
       <c r="A108" s="5"/>
       <c r="B108" s="5"/>
       <c r="C108" s="5"/>
@@ -4504,7 +4613,7 @@
       <c r="Y108" s="5"/>
       <c r="Z108" s="5"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" spans="1:26" ht="15.75" customHeight="1">
       <c r="A109" s="5"/>
       <c r="B109" s="5"/>
       <c r="C109" s="5"/>
@@ -4532,7 +4641,7 @@
       <c r="Y109" s="5"/>
       <c r="Z109" s="5"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" spans="1:26" ht="15.75" customHeight="1">
       <c r="A110" s="5"/>
       <c r="B110" s="5"/>
       <c r="C110" s="5"/>
@@ -4560,7 +4669,7 @@
       <c r="Y110" s="5"/>
       <c r="Z110" s="5"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" spans="1:26" ht="15.75" customHeight="1">
       <c r="A111" s="5"/>
       <c r="B111" s="5"/>
       <c r="C111" s="5"/>
@@ -4588,7 +4697,7 @@
       <c r="Y111" s="5"/>
       <c r="Z111" s="5"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" spans="1:26" ht="15.75" customHeight="1">
       <c r="A112" s="5"/>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
@@ -4616,7 +4725,7 @@
       <c r="Y112" s="5"/>
       <c r="Z112" s="5"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" spans="1:26" ht="15.75" customHeight="1">
       <c r="A113" s="5"/>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
@@ -4644,7 +4753,7 @@
       <c r="Y113" s="5"/>
       <c r="Z113" s="5"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" spans="1:26" ht="15.75" customHeight="1">
       <c r="A114" s="5"/>
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
@@ -4672,7 +4781,7 @@
       <c r="Y114" s="5"/>
       <c r="Z114" s="5"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" spans="1:26" ht="15.75" customHeight="1">
       <c r="A115" s="5"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
@@ -4700,7 +4809,7 @@
       <c r="Y115" s="5"/>
       <c r="Z115" s="5"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row r="116" spans="1:26" ht="15.75" customHeight="1">
       <c r="A116" s="5"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
@@ -4728,7 +4837,7 @@
       <c r="Y116" s="5"/>
       <c r="Z116" s="5"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row r="117" spans="1:26" ht="15.75" customHeight="1">
       <c r="A117" s="5"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
@@ -4756,7 +4865,7 @@
       <c r="Y117" s="5"/>
       <c r="Z117" s="5"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row r="118" spans="1:26" ht="15.75" customHeight="1">
       <c r="A118" s="5"/>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
@@ -4784,7 +4893,7 @@
       <c r="Y118" s="5"/>
       <c r="Z118" s="5"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row r="119" spans="1:26" ht="15.75" customHeight="1">
       <c r="A119" s="5"/>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
@@ -4812,7 +4921,7 @@
       <c r="Y119" s="5"/>
       <c r="Z119" s="5"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row r="120" spans="1:26" ht="15.75" customHeight="1">
       <c r="A120" s="5"/>
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
@@ -4840,7 +4949,7 @@
       <c r="Y120" s="5"/>
       <c r="Z120" s="5"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row r="121" spans="1:26" ht="15.75" customHeight="1">
       <c r="A121" s="5"/>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
@@ -4868,7 +4977,7 @@
       <c r="Y121" s="5"/>
       <c r="Z121" s="5"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row r="122" spans="1:26" ht="15.75" customHeight="1">
       <c r="A122" s="5"/>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
@@ -4896,7 +5005,7 @@
       <c r="Y122" s="5"/>
       <c r="Z122" s="5"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1">
+    <row r="123" spans="1:26" ht="15.75" customHeight="1">
       <c r="A123" s="5"/>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
@@ -4924,7 +5033,7 @@
       <c r="Y123" s="5"/>
       <c r="Z123" s="5"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1">
+    <row r="124" spans="1:26" ht="15.75" customHeight="1">
       <c r="A124" s="5"/>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
@@ -4952,7 +5061,7 @@
       <c r="Y124" s="5"/>
       <c r="Z124" s="5"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1">
+    <row r="125" spans="1:26" ht="15.75" customHeight="1">
       <c r="A125" s="5"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
@@ -4980,7 +5089,7 @@
       <c r="Y125" s="5"/>
       <c r="Z125" s="5"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1">
+    <row r="126" spans="1:26" ht="15.75" customHeight="1">
       <c r="A126" s="5"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
@@ -5008,7 +5117,7 @@
       <c r="Y126" s="5"/>
       <c r="Z126" s="5"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1">
+    <row r="127" spans="1:26" ht="15.75" customHeight="1">
       <c r="A127" s="5"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
@@ -5036,7 +5145,7 @@
       <c r="Y127" s="5"/>
       <c r="Z127" s="5"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1">
+    <row r="128" spans="1:26" ht="15.75" customHeight="1">
       <c r="A128" s="5"/>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
@@ -5064,7 +5173,7 @@
       <c r="Y128" s="5"/>
       <c r="Z128" s="5"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1">
+    <row r="129" spans="1:26" ht="15.75" customHeight="1">
       <c r="A129" s="5"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
@@ -5092,7 +5201,7 @@
       <c r="Y129" s="5"/>
       <c r="Z129" s="5"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1">
+    <row r="130" spans="1:26" ht="15.75" customHeight="1">
       <c r="A130" s="5"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
@@ -5120,7 +5229,7 @@
       <c r="Y130" s="5"/>
       <c r="Z130" s="5"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1">
+    <row r="131" spans="1:26" ht="15.75" customHeight="1">
       <c r="A131" s="5"/>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
@@ -5148,7 +5257,7 @@
       <c r="Y131" s="5"/>
       <c r="Z131" s="5"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1">
+    <row r="132" spans="1:26" ht="15.75" customHeight="1">
       <c r="A132" s="5"/>
       <c r="B132" s="5"/>
       <c r="C132" s="5"/>
@@ -5176,7 +5285,7 @@
       <c r="Y132" s="5"/>
       <c r="Z132" s="5"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1">
+    <row r="133" spans="1:26" ht="15.75" customHeight="1">
       <c r="A133" s="5"/>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
@@ -5204,7 +5313,7 @@
       <c r="Y133" s="5"/>
       <c r="Z133" s="5"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1">
+    <row r="134" spans="1:26" ht="15.75" customHeight="1">
       <c r="A134" s="5"/>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
@@ -5232,7 +5341,7 @@
       <c r="Y134" s="5"/>
       <c r="Z134" s="5"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1">
+    <row r="135" spans="1:26" ht="15.75" customHeight="1">
       <c r="A135" s="5"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>
@@ -5260,7 +5369,7 @@
       <c r="Y135" s="5"/>
       <c r="Z135" s="5"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1">
+    <row r="136" spans="1:26" ht="15.75" customHeight="1">
       <c r="A136" s="5"/>
       <c r="B136" s="5"/>
       <c r="C136" s="5"/>
@@ -5288,7 +5397,7 @@
       <c r="Y136" s="5"/>
       <c r="Z136" s="5"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1">
+    <row r="137" spans="1:26" ht="15.75" customHeight="1">
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
@@ -5316,7 +5425,7 @@
       <c r="Y137" s="5"/>
       <c r="Z137" s="5"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1">
+    <row r="138" spans="1:26" ht="15.75" customHeight="1">
       <c r="A138" s="5"/>
       <c r="B138" s="5"/>
       <c r="C138" s="5"/>
@@ -5344,7 +5453,7 @@
       <c r="Y138" s="5"/>
       <c r="Z138" s="5"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1">
+    <row r="139" spans="1:26" ht="15.75" customHeight="1">
       <c r="A139" s="5"/>
       <c r="B139" s="5"/>
       <c r="C139" s="5"/>
@@ -5372,7 +5481,7 @@
       <c r="Y139" s="5"/>
       <c r="Z139" s="5"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1">
+    <row r="140" spans="1:26" ht="15.75" customHeight="1">
       <c r="A140" s="5"/>
       <c r="B140" s="5"/>
       <c r="C140" s="5"/>
@@ -5400,7 +5509,7 @@
       <c r="Y140" s="5"/>
       <c r="Z140" s="5"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1">
+    <row r="141" spans="1:26" ht="15.75" customHeight="1">
       <c r="A141" s="5"/>
       <c r="B141" s="5"/>
       <c r="C141" s="5"/>
@@ -5428,7 +5537,7 @@
       <c r="Y141" s="5"/>
       <c r="Z141" s="5"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1">
+    <row r="142" spans="1:26" ht="15.75" customHeight="1">
       <c r="A142" s="5"/>
       <c r="B142" s="5"/>
       <c r="C142" s="5"/>
@@ -5456,7 +5565,7 @@
       <c r="Y142" s="5"/>
       <c r="Z142" s="5"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1">
+    <row r="143" spans="1:26" ht="15.75" customHeight="1">
       <c r="A143" s="5"/>
       <c r="B143" s="5"/>
       <c r="C143" s="5"/>
@@ -5484,7 +5593,7 @@
       <c r="Y143" s="5"/>
       <c r="Z143" s="5"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1">
+    <row r="144" spans="1:26" ht="15.75" customHeight="1">
       <c r="A144" s="5"/>
       <c r="B144" s="5"/>
       <c r="C144" s="5"/>
@@ -5512,7 +5621,7 @@
       <c r="Y144" s="5"/>
       <c r="Z144" s="5"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1">
+    <row r="145" spans="1:26" ht="15.75" customHeight="1">
       <c r="A145" s="5"/>
       <c r="B145" s="5"/>
       <c r="C145" s="5"/>
@@ -5540,7 +5649,7 @@
       <c r="Y145" s="5"/>
       <c r="Z145" s="5"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1">
+    <row r="146" spans="1:26" ht="15.75" customHeight="1">
       <c r="A146" s="5"/>
       <c r="B146" s="5"/>
       <c r="C146" s="5"/>
@@ -5568,7 +5677,7 @@
       <c r="Y146" s="5"/>
       <c r="Z146" s="5"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1">
+    <row r="147" spans="1:26" ht="15.75" customHeight="1">
       <c r="A147" s="5"/>
       <c r="B147" s="5"/>
       <c r="C147" s="5"/>
@@ -5596,7 +5705,7 @@
       <c r="Y147" s="5"/>
       <c r="Z147" s="5"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1">
+    <row r="148" spans="1:26" ht="15.75" customHeight="1">
       <c r="A148" s="5"/>
       <c r="B148" s="5"/>
       <c r="C148" s="5"/>
@@ -5624,7 +5733,7 @@
       <c r="Y148" s="5"/>
       <c r="Z148" s="5"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1">
+    <row r="149" spans="1:26" ht="15.75" customHeight="1">
       <c r="A149" s="5"/>
       <c r="B149" s="5"/>
       <c r="C149" s="5"/>
@@ -5652,7 +5761,7 @@
       <c r="Y149" s="5"/>
       <c r="Z149" s="5"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1">
+    <row r="150" spans="1:26" ht="15.75" customHeight="1">
       <c r="A150" s="5"/>
       <c r="B150" s="5"/>
       <c r="C150" s="5"/>
@@ -5680,7 +5789,7 @@
       <c r="Y150" s="5"/>
       <c r="Z150" s="5"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1">
+    <row r="151" spans="1:26" ht="15.75" customHeight="1">
       <c r="A151" s="5"/>
       <c r="B151" s="5"/>
       <c r="C151" s="5"/>
@@ -5708,7 +5817,7 @@
       <c r="Y151" s="5"/>
       <c r="Z151" s="5"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1">
+    <row r="152" spans="1:26" ht="15.75" customHeight="1">
       <c r="A152" s="5"/>
       <c r="B152" s="5"/>
       <c r="C152" s="5"/>
@@ -5736,7 +5845,7 @@
       <c r="Y152" s="5"/>
       <c r="Z152" s="5"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1">
+    <row r="153" spans="1:26" ht="15.75" customHeight="1">
       <c r="A153" s="5"/>
       <c r="B153" s="5"/>
       <c r="C153" s="5"/>
@@ -5764,7 +5873,7 @@
       <c r="Y153" s="5"/>
       <c r="Z153" s="5"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1">
+    <row r="154" spans="1:26" ht="15.75" customHeight="1">
       <c r="A154" s="5"/>
       <c r="B154" s="5"/>
       <c r="C154" s="5"/>
@@ -5792,7 +5901,7 @@
       <c r="Y154" s="5"/>
       <c r="Z154" s="5"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1">
+    <row r="155" spans="1:26" ht="15.75" customHeight="1">
       <c r="A155" s="5"/>
       <c r="B155" s="5"/>
       <c r="C155" s="5"/>
@@ -5820,7 +5929,7 @@
       <c r="Y155" s="5"/>
       <c r="Z155" s="5"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1">
+    <row r="156" spans="1:26" ht="15.75" customHeight="1">
       <c r="A156" s="5"/>
       <c r="B156" s="5"/>
       <c r="C156" s="5"/>
@@ -5848,7 +5957,7 @@
       <c r="Y156" s="5"/>
       <c r="Z156" s="5"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1">
+    <row r="157" spans="1:26" ht="15.75" customHeight="1">
       <c r="A157" s="5"/>
       <c r="B157" s="5"/>
       <c r="C157" s="5"/>
@@ -5876,7 +5985,7 @@
       <c r="Y157" s="5"/>
       <c r="Z157" s="5"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1">
+    <row r="158" spans="1:26" ht="15.75" customHeight="1">
       <c r="A158" s="5"/>
       <c r="B158" s="5"/>
       <c r="C158" s="5"/>
@@ -5904,7 +6013,7 @@
       <c r="Y158" s="5"/>
       <c r="Z158" s="5"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1">
+    <row r="159" spans="1:26" ht="15.75" customHeight="1">
       <c r="A159" s="5"/>
       <c r="B159" s="5"/>
       <c r="C159" s="5"/>
@@ -5932,7 +6041,7 @@
       <c r="Y159" s="5"/>
       <c r="Z159" s="5"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1">
+    <row r="160" spans="1:26" ht="15.75" customHeight="1">
       <c r="A160" s="5"/>
       <c r="B160" s="5"/>
       <c r="C160" s="5"/>
@@ -5960,7 +6069,7 @@
       <c r="Y160" s="5"/>
       <c r="Z160" s="5"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1">
+    <row r="161" spans="1:26" ht="15.75" customHeight="1">
       <c r="A161" s="5"/>
       <c r="B161" s="5"/>
       <c r="C161" s="5"/>
@@ -5988,7 +6097,7 @@
       <c r="Y161" s="5"/>
       <c r="Z161" s="5"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1">
+    <row r="162" spans="1:26" ht="15.75" customHeight="1">
       <c r="A162" s="5"/>
       <c r="B162" s="5"/>
       <c r="C162" s="5"/>
@@ -6016,7 +6125,7 @@
       <c r="Y162" s="5"/>
       <c r="Z162" s="5"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1">
+    <row r="163" spans="1:26" ht="15.75" customHeight="1">
       <c r="A163" s="5"/>
       <c r="B163" s="5"/>
       <c r="C163" s="5"/>
@@ -6044,7 +6153,7 @@
       <c r="Y163" s="5"/>
       <c r="Z163" s="5"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1">
+    <row r="164" spans="1:26" ht="15.75" customHeight="1">
       <c r="A164" s="5"/>
       <c r="B164" s="5"/>
       <c r="C164" s="5"/>
@@ -6072,7 +6181,7 @@
       <c r="Y164" s="5"/>
       <c r="Z164" s="5"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1">
+    <row r="165" spans="1:26" ht="15.75" customHeight="1">
       <c r="A165" s="5"/>
       <c r="B165" s="5"/>
       <c r="C165" s="5"/>
@@ -6100,7 +6209,7 @@
       <c r="Y165" s="5"/>
       <c r="Z165" s="5"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1">
+    <row r="166" spans="1:26" ht="15.75" customHeight="1">
       <c r="A166" s="5"/>
       <c r="B166" s="5"/>
       <c r="C166" s="5"/>
@@ -6128,7 +6237,7 @@
       <c r="Y166" s="5"/>
       <c r="Z166" s="5"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1">
+    <row r="167" spans="1:26" ht="15.75" customHeight="1">
       <c r="A167" s="5"/>
       <c r="B167" s="5"/>
       <c r="C167" s="5"/>
@@ -6156,7 +6265,7 @@
       <c r="Y167" s="5"/>
       <c r="Z167" s="5"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1">
+    <row r="168" spans="1:26" ht="15.75" customHeight="1">
       <c r="A168" s="5"/>
       <c r="B168" s="5"/>
       <c r="C168" s="5"/>
@@ -6184,7 +6293,7 @@
       <c r="Y168" s="5"/>
       <c r="Z168" s="5"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1">
+    <row r="169" spans="1:26" ht="15.75" customHeight="1">
       <c r="A169" s="5"/>
       <c r="B169" s="5"/>
       <c r="C169" s="5"/>
@@ -6212,7 +6321,7 @@
       <c r="Y169" s="5"/>
       <c r="Z169" s="5"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1">
+    <row r="170" spans="1:26" ht="15.75" customHeight="1">
       <c r="A170" s="5"/>
       <c r="B170" s="5"/>
       <c r="C170" s="5"/>
@@ -6240,7 +6349,7 @@
       <c r="Y170" s="5"/>
       <c r="Z170" s="5"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1">
+    <row r="171" spans="1:26" ht="15.75" customHeight="1">
       <c r="A171" s="5"/>
       <c r="B171" s="5"/>
       <c r="C171" s="5"/>
@@ -6268,7 +6377,7 @@
       <c r="Y171" s="5"/>
       <c r="Z171" s="5"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1">
+    <row r="172" spans="1:26" ht="15.75" customHeight="1">
       <c r="A172" s="5"/>
       <c r="B172" s="5"/>
       <c r="C172" s="5"/>
@@ -6296,7 +6405,7 @@
       <c r="Y172" s="5"/>
       <c r="Z172" s="5"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
+    <row r="173" spans="1:26" ht="15.75" customHeight="1">
       <c r="A173" s="5"/>
       <c r="B173" s="5"/>
       <c r="C173" s="5"/>
@@ -6324,7 +6433,7 @@
       <c r="Y173" s="5"/>
       <c r="Z173" s="5"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1">
+    <row r="174" spans="1:26" ht="15.75" customHeight="1">
       <c r="A174" s="5"/>
       <c r="B174" s="5"/>
       <c r="C174" s="5"/>
@@ -6352,7 +6461,7 @@
       <c r="Y174" s="5"/>
       <c r="Z174" s="5"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1">
+    <row r="175" spans="1:26" ht="15.75" customHeight="1">
       <c r="A175" s="5"/>
       <c r="B175" s="5"/>
       <c r="C175" s="5"/>
@@ -6380,7 +6489,7 @@
       <c r="Y175" s="5"/>
       <c r="Z175" s="5"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1">
+    <row r="176" spans="1:26" ht="15.75" customHeight="1">
       <c r="A176" s="5"/>
       <c r="B176" s="5"/>
       <c r="C176" s="5"/>
@@ -6408,7 +6517,7 @@
       <c r="Y176" s="5"/>
       <c r="Z176" s="5"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1">
+    <row r="177" spans="1:26" ht="15.75" customHeight="1">
       <c r="A177" s="5"/>
       <c r="B177" s="5"/>
       <c r="C177" s="5"/>
@@ -6436,7 +6545,7 @@
       <c r="Y177" s="5"/>
       <c r="Z177" s="5"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1">
+    <row r="178" spans="1:26" ht="15.75" customHeight="1">
       <c r="A178" s="5"/>
       <c r="B178" s="5"/>
       <c r="C178" s="5"/>
@@ -6464,7 +6573,7 @@
       <c r="Y178" s="5"/>
       <c r="Z178" s="5"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1">
+    <row r="179" spans="1:26" ht="15.75" customHeight="1">
       <c r="A179" s="5"/>
       <c r="B179" s="5"/>
       <c r="C179" s="5"/>
@@ -6492,7 +6601,7 @@
       <c r="Y179" s="5"/>
       <c r="Z179" s="5"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1">
+    <row r="180" spans="1:26" ht="15.75" customHeight="1">
       <c r="A180" s="5"/>
       <c r="B180" s="5"/>
       <c r="C180" s="5"/>
@@ -6520,7 +6629,7 @@
       <c r="Y180" s="5"/>
       <c r="Z180" s="5"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1">
+    <row r="181" spans="1:26" ht="15.75" customHeight="1">
       <c r="A181" s="5"/>
       <c r="B181" s="5"/>
       <c r="C181" s="5"/>
@@ -6548,7 +6657,7 @@
       <c r="Y181" s="5"/>
       <c r="Z181" s="5"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1">
+    <row r="182" spans="1:26" ht="15.75" customHeight="1">
       <c r="A182" s="5"/>
       <c r="B182" s="5"/>
       <c r="C182" s="5"/>
@@ -6576,7 +6685,7 @@
       <c r="Y182" s="5"/>
       <c r="Z182" s="5"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1">
+    <row r="183" spans="1:26" ht="15.75" customHeight="1">
       <c r="A183" s="5"/>
       <c r="B183" s="5"/>
       <c r="C183" s="5"/>
@@ -6604,7 +6713,7 @@
       <c r="Y183" s="5"/>
       <c r="Z183" s="5"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1">
+    <row r="184" spans="1:26" ht="15.75" customHeight="1">
       <c r="A184" s="5"/>
       <c r="B184" s="5"/>
       <c r="C184" s="5"/>
@@ -6632,7 +6741,7 @@
       <c r="Y184" s="5"/>
       <c r="Z184" s="5"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1">
+    <row r="185" spans="1:26" ht="15.75" customHeight="1">
       <c r="A185" s="5"/>
       <c r="B185" s="5"/>
       <c r="C185" s="5"/>
@@ -6660,7 +6769,7 @@
       <c r="Y185" s="5"/>
       <c r="Z185" s="5"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1">
+    <row r="186" spans="1:26" ht="15.75" customHeight="1">
       <c r="A186" s="5"/>
       <c r="B186" s="5"/>
       <c r="C186" s="5"/>
@@ -6688,7 +6797,7 @@
       <c r="Y186" s="5"/>
       <c r="Z186" s="5"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1">
+    <row r="187" spans="1:26" ht="15.75" customHeight="1">
       <c r="A187" s="5"/>
       <c r="B187" s="5"/>
       <c r="C187" s="5"/>
@@ -6716,7 +6825,7 @@
       <c r="Y187" s="5"/>
       <c r="Z187" s="5"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1">
+    <row r="188" spans="1:26" ht="15.75" customHeight="1">
       <c r="A188" s="5"/>
       <c r="B188" s="5"/>
       <c r="C188" s="5"/>
@@ -6744,7 +6853,7 @@
       <c r="Y188" s="5"/>
       <c r="Z188" s="5"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1">
+    <row r="189" spans="1:26" ht="15.75" customHeight="1">
       <c r="A189" s="5"/>
       <c r="B189" s="5"/>
       <c r="C189" s="5"/>
@@ -6772,7 +6881,7 @@
       <c r="Y189" s="5"/>
       <c r="Z189" s="5"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1">
+    <row r="190" spans="1:26" ht="15.75" customHeight="1">
       <c r="A190" s="5"/>
       <c r="B190" s="5"/>
       <c r="C190" s="5"/>
@@ -6800,7 +6909,7 @@
       <c r="Y190" s="5"/>
       <c r="Z190" s="5"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1">
+    <row r="191" spans="1:26" ht="15.75" customHeight="1">
       <c r="A191" s="5"/>
       <c r="B191" s="5"/>
       <c r="C191" s="5"/>
@@ -6828,7 +6937,7 @@
       <c r="Y191" s="5"/>
       <c r="Z191" s="5"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1">
+    <row r="192" spans="1:26" ht="15.75" customHeight="1">
       <c r="A192" s="5"/>
       <c r="B192" s="5"/>
       <c r="C192" s="5"/>
@@ -6856,7 +6965,7 @@
       <c r="Y192" s="5"/>
       <c r="Z192" s="5"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1">
+    <row r="193" spans="1:26" ht="15.75" customHeight="1">
       <c r="A193" s="5"/>
       <c r="B193" s="5"/>
       <c r="C193" s="5"/>
@@ -6884,7 +6993,7 @@
       <c r="Y193" s="5"/>
       <c r="Z193" s="5"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1">
+    <row r="194" spans="1:26" ht="15.75" customHeight="1">
       <c r="A194" s="5"/>
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
@@ -6912,7 +7021,7 @@
       <c r="Y194" s="5"/>
       <c r="Z194" s="5"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1">
+    <row r="195" spans="1:26" ht="15.75" customHeight="1">
       <c r="A195" s="5"/>
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
@@ -6940,7 +7049,7 @@
       <c r="Y195" s="5"/>
       <c r="Z195" s="5"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1">
+    <row r="196" spans="1:26" ht="15.75" customHeight="1">
       <c r="A196" s="5"/>
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
@@ -6968,7 +7077,7 @@
       <c r="Y196" s="5"/>
       <c r="Z196" s="5"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1">
+    <row r="197" spans="1:26" ht="15.75" customHeight="1">
       <c r="A197" s="5"/>
       <c r="B197" s="5"/>
       <c r="C197" s="5"/>
@@ -6996,7 +7105,7 @@
       <c r="Y197" s="5"/>
       <c r="Z197" s="5"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1">
+    <row r="198" spans="1:26" ht="15.75" customHeight="1">
       <c r="A198" s="5"/>
       <c r="B198" s="5"/>
       <c r="C198" s="5"/>
@@ -7024,7 +7133,7 @@
       <c r="Y198" s="5"/>
       <c r="Z198" s="5"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1">
+    <row r="199" spans="1:26" ht="15.75" customHeight="1">
       <c r="A199" s="5"/>
       <c r="B199" s="5"/>
       <c r="C199" s="5"/>
@@ -7052,7 +7161,7 @@
       <c r="Y199" s="5"/>
       <c r="Z199" s="5"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1">
+    <row r="200" spans="1:26" ht="15.75" customHeight="1">
       <c r="A200" s="5"/>
       <c r="B200" s="5"/>
       <c r="C200" s="5"/>
@@ -7080,7 +7189,7 @@
       <c r="Y200" s="5"/>
       <c r="Z200" s="5"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1">
+    <row r="201" spans="1:26" ht="15.75" customHeight="1">
       <c r="A201" s="5"/>
       <c r="B201" s="5"/>
       <c r="C201" s="5"/>
@@ -7108,7 +7217,7 @@
       <c r="Y201" s="5"/>
       <c r="Z201" s="5"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1">
+    <row r="202" spans="1:26" ht="15.75" customHeight="1">
       <c r="A202" s="5"/>
       <c r="B202" s="5"/>
       <c r="C202" s="5"/>
@@ -7136,7 +7245,7 @@
       <c r="Y202" s="5"/>
       <c r="Z202" s="5"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1">
+    <row r="203" spans="1:26" ht="15.75" customHeight="1">
       <c r="A203" s="5"/>
       <c r="B203" s="5"/>
       <c r="C203" s="5"/>
@@ -7164,7 +7273,7 @@
       <c r="Y203" s="5"/>
       <c r="Z203" s="5"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1">
+    <row r="204" spans="1:26" ht="15.75" customHeight="1">
       <c r="A204" s="5"/>
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
@@ -7192,7 +7301,7 @@
       <c r="Y204" s="5"/>
       <c r="Z204" s="5"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1">
+    <row r="205" spans="1:26" ht="15.75" customHeight="1">
       <c r="A205" s="5"/>
       <c r="B205" s="5"/>
       <c r="C205" s="5"/>
@@ -7220,7 +7329,7 @@
       <c r="Y205" s="5"/>
       <c r="Z205" s="5"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1">
+    <row r="206" spans="1:26" ht="15.75" customHeight="1">
       <c r="A206" s="5"/>
       <c r="B206" s="5"/>
       <c r="C206" s="5"/>
@@ -7248,7 +7357,7 @@
       <c r="Y206" s="5"/>
       <c r="Z206" s="5"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1">
+    <row r="207" spans="1:26" ht="15.75" customHeight="1">
       <c r="A207" s="5"/>
       <c r="B207" s="5"/>
       <c r="C207" s="5"/>
@@ -7276,7 +7385,7 @@
       <c r="Y207" s="5"/>
       <c r="Z207" s="5"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1">
+    <row r="208" spans="1:26" ht="15.75" customHeight="1">
       <c r="A208" s="5"/>
       <c r="B208" s="5"/>
       <c r="C208" s="5"/>
@@ -7304,7 +7413,7 @@
       <c r="Y208" s="5"/>
       <c r="Z208" s="5"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1">
+    <row r="209" spans="1:26" ht="15.75" customHeight="1">
       <c r="A209" s="5"/>
       <c r="B209" s="5"/>
       <c r="C209" s="5"/>
@@ -7332,7 +7441,7 @@
       <c r="Y209" s="5"/>
       <c r="Z209" s="5"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1">
+    <row r="210" spans="1:26" ht="15.75" customHeight="1">
       <c r="A210" s="5"/>
       <c r="B210" s="5"/>
       <c r="C210" s="5"/>
@@ -7360,7 +7469,7 @@
       <c r="Y210" s="5"/>
       <c r="Z210" s="5"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1">
+    <row r="211" spans="1:26" ht="15.75" customHeight="1">
       <c r="A211" s="5"/>
       <c r="B211" s="5"/>
       <c r="C211" s="5"/>
@@ -7388,7 +7497,7 @@
       <c r="Y211" s="5"/>
       <c r="Z211" s="5"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1">
+    <row r="212" spans="1:26" ht="15.75" customHeight="1">
       <c r="A212" s="5"/>
       <c r="B212" s="5"/>
       <c r="C212" s="5"/>
@@ -7416,7 +7525,7 @@
       <c r="Y212" s="5"/>
       <c r="Z212" s="5"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1">
+    <row r="213" spans="1:26" ht="15.75" customHeight="1">
       <c r="A213" s="5"/>
       <c r="B213" s="5"/>
       <c r="C213" s="5"/>
@@ -7444,7 +7553,7 @@
       <c r="Y213" s="5"/>
       <c r="Z213" s="5"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1">
+    <row r="214" spans="1:26" ht="15.75" customHeight="1">
       <c r="A214" s="5"/>
       <c r="B214" s="5"/>
       <c r="C214" s="5"/>
@@ -7472,7 +7581,7 @@
       <c r="Y214" s="5"/>
       <c r="Z214" s="5"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1">
+    <row r="215" spans="1:26" ht="15.75" customHeight="1">
       <c r="A215" s="5"/>
       <c r="B215" s="5"/>
       <c r="C215" s="5"/>
@@ -7500,7 +7609,7 @@
       <c r="Y215" s="5"/>
       <c r="Z215" s="5"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1">
+    <row r="216" spans="1:26" ht="15.75" customHeight="1">
       <c r="A216" s="5"/>
       <c r="B216" s="5"/>
       <c r="C216" s="5"/>
@@ -7528,7 +7637,7 @@
       <c r="Y216" s="5"/>
       <c r="Z216" s="5"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1">
+    <row r="217" spans="1:26" ht="15.75" customHeight="1">
       <c r="A217" s="5"/>
       <c r="B217" s="5"/>
       <c r="C217" s="5"/>
@@ -7556,7 +7665,7 @@
       <c r="Y217" s="5"/>
       <c r="Z217" s="5"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1">
+    <row r="218" spans="1:26" ht="15.75" customHeight="1">
       <c r="A218" s="5"/>
       <c r="B218" s="5"/>
       <c r="C218" s="5"/>
@@ -7584,7 +7693,7 @@
       <c r="Y218" s="5"/>
       <c r="Z218" s="5"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1">
+    <row r="219" spans="1:26" ht="15.75" customHeight="1">
       <c r="A219" s="5"/>
       <c r="B219" s="5"/>
       <c r="C219" s="5"/>
@@ -7612,7 +7721,7 @@
       <c r="Y219" s="5"/>
       <c r="Z219" s="5"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1">
+    <row r="220" spans="1:26" ht="15.75" customHeight="1">
       <c r="A220" s="5"/>
       <c r="B220" s="5"/>
       <c r="C220" s="5"/>
@@ -7640,7 +7749,7 @@
       <c r="Y220" s="5"/>
       <c r="Z220" s="5"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1">
+    <row r="221" spans="1:26" ht="15.75" customHeight="1">
       <c r="A221" s="7"/>
       <c r="B221" s="7"/>
       <c r="C221" s="7"/>
@@ -7668,7 +7777,7 @@
       <c r="Y221" s="7"/>
       <c r="Z221" s="7"/>
     </row>
-    <row r="222" ht="15.75" customHeight="1">
+    <row r="222" spans="1:26" ht="15.75" customHeight="1">
       <c r="A222" s="7"/>
       <c r="B222" s="7"/>
       <c r="C222" s="7"/>
@@ -7696,7 +7805,7 @@
       <c r="Y222" s="7"/>
       <c r="Z222" s="7"/>
     </row>
-    <row r="223" ht="15.75" customHeight="1">
+    <row r="223" spans="1:26" ht="15.75" customHeight="1">
       <c r="A223" s="7"/>
       <c r="B223" s="7"/>
       <c r="C223" s="7"/>
@@ -7724,7 +7833,7 @@
       <c r="Y223" s="7"/>
       <c r="Z223" s="7"/>
     </row>
-    <row r="224" ht="15.75" customHeight="1">
+    <row r="224" spans="1:26" ht="15.75" customHeight="1">
       <c r="A224" s="7"/>
       <c r="B224" s="7"/>
       <c r="C224" s="7"/>
@@ -7752,7 +7861,7 @@
       <c r="Y224" s="7"/>
       <c r="Z224" s="7"/>
     </row>
-    <row r="225" ht="15.75" customHeight="1">
+    <row r="225" spans="1:26" ht="15.75" customHeight="1">
       <c r="A225" s="7"/>
       <c r="B225" s="7"/>
       <c r="C225" s="7"/>
@@ -7780,7 +7889,7 @@
       <c r="Y225" s="7"/>
       <c r="Z225" s="7"/>
     </row>
-    <row r="226" ht="15.75" customHeight="1">
+    <row r="226" spans="1:26" ht="15.75" customHeight="1">
       <c r="A226" s="7"/>
       <c r="B226" s="7"/>
       <c r="C226" s="7"/>
@@ -7808,7 +7917,7 @@
       <c r="Y226" s="7"/>
       <c r="Z226" s="7"/>
     </row>
-    <row r="227" ht="15.75" customHeight="1">
+    <row r="227" spans="1:26" ht="15.75" customHeight="1">
       <c r="A227" s="7"/>
       <c r="B227" s="7"/>
       <c r="C227" s="7"/>
@@ -7836,7 +7945,7 @@
       <c r="Y227" s="7"/>
       <c r="Z227" s="7"/>
     </row>
-    <row r="228" ht="15.75" customHeight="1">
+    <row r="228" spans="1:26" ht="15.75" customHeight="1">
       <c r="A228" s="7"/>
       <c r="B228" s="7"/>
       <c r="C228" s="7"/>
@@ -7864,7 +7973,7 @@
       <c r="Y228" s="7"/>
       <c r="Z228" s="7"/>
     </row>
-    <row r="229" ht="15.75" customHeight="1">
+    <row r="229" spans="1:26" ht="15.75" customHeight="1">
       <c r="A229" s="7"/>
       <c r="B229" s="7"/>
       <c r="C229" s="7"/>
@@ -7892,7 +8001,7 @@
       <c r="Y229" s="7"/>
       <c r="Z229" s="7"/>
     </row>
-    <row r="230" ht="15.75" customHeight="1">
+    <row r="230" spans="1:26" ht="15.75" customHeight="1">
       <c r="A230" s="7"/>
       <c r="B230" s="7"/>
       <c r="C230" s="7"/>
@@ -7920,16 +8029,16 @@
       <c r="Y230" s="7"/>
       <c r="Z230" s="7"/>
     </row>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="231" spans="1:26" ht="15.75" customHeight="1"/>
+    <row r="232" spans="1:26" ht="15.75" customHeight="1"/>
+    <row r="233" spans="1:26" ht="15.75" customHeight="1"/>
+    <row r="234" spans="1:26" ht="15.75" customHeight="1"/>
+    <row r="235" spans="1:26" ht="15.75" customHeight="1"/>
+    <row r="236" spans="1:26" ht="15.75" customHeight="1"/>
+    <row r="237" spans="1:26" ht="15.75" customHeight="1"/>
+    <row r="238" spans="1:26" ht="15.75" customHeight="1"/>
+    <row r="239" spans="1:26" ht="15.75" customHeight="1"/>
+    <row r="240" spans="1:26" ht="15.75" customHeight="1"/>
     <row r="241" ht="15.75" customHeight="1"/>
     <row r="242" ht="15.75" customHeight="1"/>
     <row r="243" ht="15.75" customHeight="1"/>
@@ -8691,9 +8800,8 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>